--- a/docs/reports/Shelly_Pack_Wholesale.xlsx
+++ b/docs/reports/Shelly_Pack_Wholesale.xlsx
@@ -21538,7 +21538,7 @@
     <row r="21">
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Generated by Shelly on 29 Sep 2026 22:17</t>
+          <t>Generated by Shelly on 03 Oct 2026 05:37</t>
         </is>
       </c>
     </row>

--- a/docs/reports/Shelly_Pack_Wholesale.xlsx
+++ b/docs/reports/Shelly_Pack_Wholesale.xlsx
@@ -21538,7 +21538,7 @@
     <row r="21">
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Generated by Shelly on 03 Oct 2026 05:37</t>
+          <t>Generated by Shelly on 03 Oct 2026 05:51</t>
         </is>
       </c>
     </row>

--- a/docs/reports/Shelly_Pack_Wholesale.xlsx
+++ b/docs/reports/Shelly_Pack_Wholesale.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pivot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lookup" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer profitability 90 days" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Receivables ageing" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fill rate &amp; OTIF" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Model" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pivot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Raw" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Lookup" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Actions" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Customer profitability 90 days" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Receivables ageing" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Fill rate &amp; OTIF" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Notes" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="SelCat">Dashboard!$B$6</definedName>
@@ -29,7 +29,7 @@
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
   <pivotCaches>
-    <pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="1" r:id="rId12"/>
+    <pivotCache cacheId="1" r:id="rId12"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -306,13 +306,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -334,10 +334,10 @@
             <v>Gross margin</v>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A8FB8"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="2A8FB8"/>
               </a:solidFill>
@@ -395,13 +395,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -422,7 +422,7 @@
             <v>Revenue</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="2A8FB8"/>
               </a:solidFill>
@@ -432,7 +432,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -504,7 +504,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -519,9 +519,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -541,9 +541,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21538,7 +21538,7 @@
     <row r="21">
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Generated by Shelly on 03 Oct 2026 05:51</t>
+          <t>Generated by Shelly on 04 Oct 2026 20:46</t>
         </is>
       </c>
     </row>

--- a/docs/reports/Shelly_Pack_Wholesale.xlsx
+++ b/docs/reports/Shelly_Pack_Wholesale.xlsx
@@ -21538,7 +21538,7 @@
     <row r="21">
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Generated by Shelly on 04 Oct 2026 20:46</t>
+          <t>Generated by Shelly on 11 Oct 2026 21:21</t>
         </is>
       </c>
     </row>
